--- a/docs/sample_template.xlsx
+++ b/docs/sample_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_github\excel-template-viz\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65293F27-EAB6-4521-9361-0BCB9FC12D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6AA3DD-D8F5-4354-87DD-0BC3CD98DA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6840" yWindow="3150" windowWidth="28800" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input_sheet" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>Discipline</t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
     <t>Sign</t>
   </si>
   <si>
@@ -83,6 +80,10 @@
   </si>
   <si>
     <t>Effective Date</t>
+  </si>
+  <si>
+    <t>Effective_Date</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -292,10 +293,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -303,22 +304,22 @@
         <v>8129</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="2">
         <v>46053</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -326,22 +327,22 @@
         <v>250</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F3" s="2">
         <v>46053</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -368,7 +369,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -384,12 +385,12 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
         <v>46023</v>
@@ -400,7 +401,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -416,12 +417,12 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>46053</v>
